--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Github\himanshu9084.github.io\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Github\himanshu9084.github.io\js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDF87C2-51AC-4142-B1E2-0BD2032169AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53162600-B502-4A9B-8CC3-29AE9FAB5882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>date</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>code_url</t>
+  </si>
+  <si>
+    <t>arxiv_url</t>
   </si>
   <si>
     <t>Continual Segmentation under Joint Nonstationarity</t>
@@ -479,10 +482,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -498,53 +501,56 @@
       <c r="E1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2025</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +576,7 @@
         <v>2019</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -593,18 +599,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Github\himanshu9084.github.io\js\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Github\himanshu9084.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53162600-B502-4A9B-8CC3-29AE9FAB5882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C272EC-61B1-4A45-B450-4F25F05260C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>date</t>
   </si>
@@ -91,16 +91,13 @@
     <t>AIR 107, GATE 2019 — Computer Science, 99.89 percentile among ~1 lakh candidates.</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>[Placeholder] Reviewer — [Conference / Workshop name].</t>
-  </si>
-  <si>
-    <t>[Placeholder] Volunteer / outreach activity.</t>
-  </si>
-  <si>
     <t>https://icml.cc/virtual/2026/poster/61083</t>
+  </si>
+  <si>
+    <t>Webinar at Dept. of CSIT, SOA University on Recent Advancements in AI.</t>
+  </si>
+  <si>
+    <t>ML &amp; AI Webinar at Government Engineering College, Nawada to an audience of about 100, including professors and students and latest AI methods.</t>
   </si>
 </sst>
 </file>
@@ -136,8 +133,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,7 +514,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -598,19 +596,19 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>22</v>
+      <c r="A2" s="1">
+        <v>45139</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>44562</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Github\himanshu9084.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C272EC-61B1-4A45-B450-4F25F05260C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EE1FF0-6B95-4A4E-BEB9-CBAFFDE2EE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>date</t>
   </si>
@@ -97,7 +97,16 @@
     <t>Webinar at Dept. of CSIT, SOA University on Recent Advancements in AI.</t>
   </si>
   <si>
-    <t>ML &amp; AI Webinar at Government Engineering College, Nawada to an audience of about 100, including professors and students and latest AI methods.</t>
+    <t>ML &amp; AI Webinar at Government Engineering College, Nawada to an audience of about 100, including professors and students on latest AI methods.</t>
+  </si>
+  <si>
+    <t>poster_url</t>
+  </si>
+  <si>
+    <t>https://www.gecnawada.org.in/one-day-webinar-on-artificial-intelligence-and-machine-learning-on-24th-august-2023/</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sa2a4m5YsUYCr0Y2x8j5cEgS7HvcVLFE/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -584,31 +593,40 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45139</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>44562</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Github\himanshu9084.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EE1FF0-6B95-4A4E-BEB9-CBAFFDE2EE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87396932-2DC8-4520-994F-1D6B14E72BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>date</t>
   </si>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>https://www.gecnawada.org.in/one-day-webinar-on-artificial-intelligence-and-machine-learning-on-24th-august-2023/</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1sa2a4m5YsUYCr0Y2x8j5cEgS7HvcVLFE/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -625,9 +622,6 @@
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
